--- a/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="89">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:43:57+00:00</t>
+    <t>2026-09-02T12:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>FRLMRelatedPerson.name</t>
+  </si>
+  <si>
+    <t>FRLMHumanName</t>
   </si>
   <si>
     <t>Person.name</t>
@@ -678,12 +681,14 @@
       <c r="A3" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" t="s" s="2">
+        <v>45</v>
+      </c>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -716,7 +721,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -725,7 +730,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -733,79 +738,79 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -847,7 +852,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -862,20 +867,20 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -883,25 +888,27 @@
       <c r="A5" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>45</v>
+      </c>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -914,7 +921,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -927,7 +934,7 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -940,98 +947,98 @@
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1064,7 +1071,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1073,7 +1080,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1081,53 +1088,53 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="2"/>
     </row>

--- a/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:54:48+00:00</t>
+    <t>2026-09-02T15:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:48:56+00:00</t>
+    <t>2026-09-03T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:02:14+00:00</t>
+    <t>2026-09-03T10:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:35:28+00:00</t>
+    <t>2026-09-04T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
